--- a/data/mapper.xlsx
+++ b/data/mapper.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10111"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/18b3d1ec65516a7e/UCR_Projects/Projekte/PEXInteraktom/Manuskript/Julia_Analysen/results/translations/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/18b3d1ec65516a7e/UCR_Projects/Projekte/PEXInteraktom/R_notebooks/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_86D23DD446592EC20A160B6E2BDCC937502C8586" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8CF6947-04AA-9942-AB09-C2150BA6D04D}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_86D23DD446592EC20A160B6E2BDCC937502C8586" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2CF4584-0234-424C-8AEE-F7A7F2EE6A12}"/>
   <bookViews>
-    <workbookView xWindow="3020" yWindow="4680" windowWidth="29300" windowHeight="20900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3020" yWindow="1340" windowWidth="29300" windowHeight="20900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="337">
   <si>
     <t>Gene_name_custom</t>
   </si>
@@ -1025,6 +1025,12 @@
   </si>
   <si>
     <t>P50542-1|A0A0S2Z4H1|B4DR50</t>
+  </si>
+  <si>
+    <t>MTARC2</t>
+  </si>
+  <si>
+    <t>PTGR3</t>
   </si>
 </sst>
 </file>
@@ -1106,9 +1112,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1146,9 +1152,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1181,26 +1187,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1233,26 +1222,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2959,7 +2931,7 @@
         <v>173</v>
       </c>
       <c r="C60" t="s">
-        <v>66</v>
+        <v>335</v>
       </c>
       <c r="D60" t="s">
         <v>280</v>
@@ -4238,7 +4210,7 @@
         <v>221</v>
       </c>
       <c r="C110" t="s">
-        <v>116</v>
+        <v>336</v>
       </c>
       <c r="D110" t="s">
         <v>325</v>
